--- a/Design/Excel/ET/Datas/Product/GridManualRecipeConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/GridManualRecipeConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1302,6 +1302,38 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design/Excel/ET/Datas/Product/GridManualRecipeConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/GridManualRecipeConfig.xlsx
@@ -939,503 +939,521 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <x:col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <x:col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <x:col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <x:col min="11" max="16384" width="9" style="2" customWidth="0"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InputDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OutputDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RequiredTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="str">
-        <x:v>InputDefinitionIds</x:v>
-      </x:c>
-      <x:c r="H1" t="str">
-        <x:v>InputCounts</x:v>
-      </x:c>
-      <x:c r="I1" t="str">
-        <x:v>ContainerDefinitionId</x:v>
-      </x:c>
-      <x:c r="J1" t="str">
-        <x:v>LastInputDefinitionId</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>GridManualMode</x:v>
-      </x:c>
-      <x:c r="D2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>(list#sep=,),int</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>(list#sep=,),int</x:v>
-      </x:c>
-      <x:c r="I2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="J2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InputDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OutputDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RequiredTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" t="str">
-        <x:v>精确组装投入</x:v>
-      </x:c>
-      <x:c r="H3" t="str">
-        <x:v>精确组装份数</x:v>
-      </x:c>
-      <x:c r="I3" t="str">
-        <x:v>组装载具</x:v>
-      </x:c>
-      <x:c r="J3" t="str">
-        <x:v>最后投入的定义（0为不限顺序）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">60</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" t="str"/>
-      <x:c r="H4" t="str"/>
-      <x:c r="I4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">60</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" t="str"/>
-      <x:c r="H5" t="str"/>
-      <x:c r="I5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">15</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">16</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">60</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" t="str"/>
-      <x:c r="H6" t="str"/>
-      <x:c r="I6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str"/>
-      <x:c r="B7" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E7" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F7" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G7" t="str"/>
-      <x:c r="H7" t="str"/>
-      <x:c r="I7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str"/>
-      <x:c r="B8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F8" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G8" t="str"/>
-      <x:c r="H8" t="str"/>
-      <x:c r="I8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str"/>
-      <x:c r="B9" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F9" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G9" t="str">
-        <x:v>2,23,25</x:v>
-      </x:c>
-      <x:c r="H9" t="str">
-        <x:v>1,1,1</x:v>
-      </x:c>
-      <x:c r="I9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str"/>
-      <x:c r="B10" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E10" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F10" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G10" t="str">
-        <x:v>2,23,25,26</x:v>
-      </x:c>
-      <x:c r="H10" t="str">
-        <x:v>1,1,1,1</x:v>
-      </x:c>
-      <x:c r="I10" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str"/>
-      <x:c r="B11" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F11" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G11" t="str">
-        <x:v>32,34</x:v>
-      </x:c>
-      <x:c r="H11" t="str">
-        <x:v>1,1</x:v>
-      </x:c>
-      <x:c r="I11" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str"/>
-      <x:c r="B12" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F12" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G12" t="str">
-        <x:v>36,37,9</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>1,1,1</x:v>
-      </x:c>
-      <x:c r="I12" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str"/>
-      <x:c r="B13" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F13" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G13" t="str">
-        <x:v>56,57</x:v>
-      </x:c>
-      <x:c r="H13" t="str">
-        <x:v>1,2</x:v>
-      </x:c>
-      <x:c r="I13" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str"/>
-      <x:c r="B14" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C14" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E14" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F14" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G14" t="str">
-        <x:v>56,57,58</x:v>
-      </x:c>
-      <x:c r="H14" t="str">
-        <x:v>1,1,1</x:v>
-      </x:c>
-      <x:c r="I14" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J14" t="n">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InputDefinitionId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OutputDefinitionId</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RequiredTicks</t>
+        </is>
+      </c>
+      <c r="G1" t="str">
+        <v>InputDefinitionIds</v>
+      </c>
+      <c r="H1" t="str">
+        <v>InputCounts</v>
+      </c>
+      <c r="I1" t="str">
+        <v>ContainerDefinitionId</v>
+      </c>
+      <c r="J1" t="str">
+        <v>LastInputDefinitionId</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GridManualMode</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="G2" t="str">
+        <v>(list#sep=,),int</v>
+      </c>
+      <c r="H2" t="str">
+        <v>(list#sep=,),int</v>
+      </c>
+      <c r="I2" t="str">
+        <v>int</v>
+      </c>
+      <c r="J2" t="str">
+        <v>int</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mode</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InputDefinitionId</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OutputDefinitionId</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RequiredTicks</t>
+        </is>
+      </c>
+      <c r="G3" t="str">
+        <v>精确组装投入</v>
+      </c>
+      <c r="H3" t="str">
+        <v>精确组装份数</v>
+      </c>
+      <c r="I3" t="str">
+        <v>组装载具</v>
+      </c>
+      <c r="J3" t="str">
+        <v>最后投入的定义（0为不限顺序）</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chop</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c r="G4" t="str"/>
+      <c r="H4" t="str"/>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Beat</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c r="G5" t="str"/>
+      <c r="H5" t="str"/>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chop</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
+      <c r="G6" t="str"/>
+      <c r="H6" t="str"/>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str"/>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chop</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E7" t="n">
+        <v>23</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="str"/>
+      <c r="H7" t="str"/>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str"/>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chop</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" t="str"/>
+      <c r="H8" t="str"/>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str"/>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>27</v>
+      </c>
+      <c r="F9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2,23,25</v>
+      </c>
+      <c r="H9" t="str">
+        <v>1,1,1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str"/>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>28</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2,23,25,26</v>
+      </c>
+      <c r="H10" t="str">
+        <v>1,1,1,1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str"/>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>38</v>
+      </c>
+      <c r="F11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G11" t="str">
+        <v>32,34</v>
+      </c>
+      <c r="H11" t="str">
+        <v>1,1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str"/>
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>39</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G12" t="str">
+        <v>36,37,9</v>
+      </c>
+      <c r="H12" t="str">
+        <v>1,1,1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str"/>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G13" t="str">
+        <v>56,57</v>
+      </c>
+      <c r="H13" t="str">
+        <v>1,2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>59</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str"/>
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Assembly</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>61</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" t="str">
+        <v>56,57,58</v>
+      </c>
+      <c r="H14" t="str">
+        <v>1,1,1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>59</v>
+      </c>
+      <c r="J14" t="n">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>